--- a/xls/square_16_quad4_11.xlsx
+++ b/xls/square_16_quad4_11.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>144</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>289</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>243</v>
+      </c>
+      <c r="I9">
+        <v>4.608019683093116</v>
+      </c>
+      <c r="J9">
+        <v>1.702759630486757</v>
+      </c>
+      <c r="K9">
+        <v>1.7029362119124178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>144</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>289</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>121</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>300</v>
+      </c>
+      <c r="I10">
+        <v>2.137210940250439</v>
+      </c>
+      <c r="J10">
+        <v>0.29728814819006344</v>
+      </c>
+      <c r="K10">
+        <v>0.4526951245753247</v>
+      </c>
+    </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>11</v>
@@ -482,13 +552,13 @@
         <v>363</v>
       </c>
       <c r="I11">
-        <v>1.3267312788613017</v>
+        <v>0.5348097447391692</v>
       </c>
       <c r="J11">
-        <v>-1.160570936121709</v>
+        <v>-1.0896307412053043</v>
       </c>
       <c r="K11">
-        <v>-0.7262373925622875</v>
+        <v>-0.8910704129478216</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -517,13 +587,13 @@
         <v>432</v>
       </c>
       <c r="I12">
-        <v>-1.4926542224351396</v>
+        <v>-1.168558226808528</v>
       </c>
       <c r="J12">
-        <v>-1.468420638848534</v>
+        <v>-1.2097277699243083</v>
       </c>
       <c r="K12">
-        <v>-1.1530073775130854</v>
+        <v>-1.1377196291997247</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -552,13 +622,13 @@
         <v>507</v>
       </c>
       <c r="I13">
-        <v>-1.5585254781324756</v>
+        <v>-1.2420797703758075</v>
       </c>
       <c r="J13">
-        <v>-1.5746033544303637</v>
+        <v>-1.2875859384201223</v>
       </c>
       <c r="K13">
-        <v>-1.2334778156714856</v>
+        <v>-1.2154151536712163</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -587,13 +657,13 @@
         <v>588</v>
       </c>
       <c r="I14">
-        <v>-1.6307578350889549</v>
+        <v>-1.3027019343927282</v>
       </c>
       <c r="J14">
-        <v>-1.656287910090612</v>
+        <v>-1.3488292571951959</v>
       </c>
       <c r="K14">
-        <v>-1.2589263731415459</v>
+        <v>-1.2496215434569722</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -622,13 +692,13 @@
         <v>675</v>
       </c>
       <c r="I15">
-        <v>-1.7178861971084634</v>
+        <v>-1.3664336722750952</v>
       </c>
       <c r="J15">
-        <v>-1.6789265684847356</v>
+        <v>-1.4041660936794615</v>
       </c>
       <c r="K15">
-        <v>-0.6905046571395288</v>
+        <v>-0.8033525478581974</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -657,13 +727,13 @@
         <v>768</v>
       </c>
       <c r="I16">
-        <v>-1.8316043927736834</v>
+        <v>-1.4739153107498917</v>
       </c>
       <c r="J16">
-        <v>-1.6896931376280608</v>
+        <v>-1.4969931201161888</v>
       </c>
       <c r="K16">
-        <v>-0.6106715761077831</v>
+        <v>-0.7134900426487811</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -692,13 +762,13 @@
         <v>867</v>
       </c>
       <c r="I17">
-        <v>-1.3031347639871558</v>
+        <v>-1.5728356231682423</v>
       </c>
       <c r="J17">
-        <v>-0.9765955766813817</v>
+        <v>-1.2544001294004912</v>
       </c>
       <c r="K17">
-        <v>3.4542320131059907</v>
+        <v>3.2502702000715704</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -727,13 +797,13 @@
         <v>972</v>
       </c>
       <c r="I18">
-        <v>-0.2206518129378161</v>
+        <v>-0.18224932261731092</v>
       </c>
       <c r="J18">
-        <v>-0.20010679384850505</v>
+        <v>-0.12343708254774219</v>
       </c>
       <c r="K18">
-        <v>3.9114510505453386</v>
+        <v>4.4920207484257615</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -762,13 +832,13 @@
         <v>1083</v>
       </c>
       <c r="I19">
-        <v>-0.12855228452437595</v>
+        <v>-0.0019585787305604445</v>
       </c>
       <c r="J19">
-        <v>-0.1254496887587214</v>
+        <v>-0.0023164820502700584</v>
       </c>
       <c r="K19">
-        <v>3.8354293499044885</v>
+        <v>4.076251092755782</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -797,13 +867,13 @@
         <v>1200</v>
       </c>
       <c r="I20">
-        <v>-0.046687853126658636</v>
+        <v>-0.0005223141172719473</v>
       </c>
       <c r="J20">
-        <v>-0.04153875182557364</v>
+        <v>-0.0004674047271487284</v>
       </c>
       <c r="K20">
-        <v>3.701722115016882</v>
+        <v>3.686132939488409</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -832,13 +902,13 @@
         <v>1323</v>
       </c>
       <c r="I21">
-        <v>-4.693992287977208e-5</v>
+        <v>-9.604502558732516e-7</v>
       </c>
       <c r="J21">
-        <v>-3.0141519995965014e-5</v>
+        <v>-5.804751408310095e-7</v>
       </c>
       <c r="K21">
-        <v>2.0157534942197093</v>
+        <v>2.060403217498874</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -867,13 +937,13 @@
         <v>1452</v>
       </c>
       <c r="I22">
-        <v>-0.00264152997933846</v>
+        <v>-2.9275183939824926e-5</v>
       </c>
       <c r="J22">
-        <v>-0.0019990466709734235</v>
+        <v>-2.254792228688378e-5</v>
       </c>
       <c r="K22">
-        <v>3.012705074680531</v>
+        <v>2.9901221223966488</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -902,13 +972,13 @@
         <v>1587</v>
       </c>
       <c r="I23">
-        <v>-3.6799024574902187e-6</v>
+        <v>-1.0507094077800926e-7</v>
       </c>
       <c r="J23">
-        <v>-3.144618882801525e-6</v>
+        <v>-7.089335174293325e-8</v>
       </c>
       <c r="K23">
-        <v>1.7358276033082798</v>
+        <v>1.7850817065441211</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -937,13 +1007,13 @@
         <v>1728</v>
       </c>
       <c r="I24">
-        <v>-3.0575690105017656e-6</v>
+        <v>-2.999824465783421e-8</v>
       </c>
       <c r="J24">
-        <v>-6.048198380460115e-6</v>
+        <v>-6.313135374190084e-8</v>
       </c>
       <c r="K24">
-        <v>1.9276219929618614</v>
+        <v>1.9124208873122421</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -972,13 +1042,13 @@
         <v>1875</v>
       </c>
       <c r="I25">
-        <v>3.0869564802719134e-7</v>
+        <v>1.2659139367150782e-9</v>
       </c>
       <c r="J25">
-        <v>-1.096759004688996e-6</v>
+        <v>-1.3554035823582873e-8</v>
       </c>
       <c r="K25">
-        <v>1.7025856800302437</v>
+        <v>1.6944175402291581</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1007,13 +1077,13 @@
         <v>2028</v>
       </c>
       <c r="I26">
-        <v>-1.1400171246704282e-6</v>
+        <v>-1.0465646697683538e-8</v>
       </c>
       <c r="J26">
-        <v>-1.6719535032416081e-6</v>
+        <v>-1.823003794155775e-8</v>
       </c>
       <c r="K26">
-        <v>1.686356498589056</v>
+        <v>1.684092172034898</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1042,13 +1112,13 @@
         <v>2187</v>
       </c>
       <c r="I27">
-        <v>-3.215515236300995e-7</v>
+        <v>-4.5489632060365074e-9</v>
       </c>
       <c r="J27">
-        <v>-7.054798306754424e-7</v>
+        <v>-1.0057370786007679e-8</v>
       </c>
       <c r="K27">
-        <v>1.5033047263662949</v>
+        <v>1.5515192534895998</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1077,13 +1147,13 @@
         <v>2352</v>
       </c>
       <c r="I28">
-        <v>-3.4864353521194997e-7</v>
+        <v>-4.540185222314858e-9</v>
       </c>
       <c r="J28">
-        <v>-5.522376264849334e-7</v>
+        <v>-7.85423344648288e-9</v>
       </c>
       <c r="K28">
-        <v>1.4227335745743093</v>
+        <v>1.473893459297905</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1112,13 +1182,13 @@
         <v>2523</v>
       </c>
       <c r="I29">
-        <v>-2.7249839512464147e-7</v>
+        <v>-3.5992194477159084e-9</v>
       </c>
       <c r="J29">
-        <v>-4.7383656743505063e-7</v>
+        <v>-6.4998522766245405e-9</v>
       </c>
       <c r="K29">
-        <v>1.3969342576934833</v>
+        <v>1.437414974301002</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1147,13 +1217,13 @@
         <v>2700</v>
       </c>
       <c r="I30">
-        <v>-1.670657906598044e-7</v>
+        <v>-2.355017285319823e-9</v>
       </c>
       <c r="J30">
-        <v>-4.6186126585030606e-7</v>
+        <v>-6.0964540335039014e-9</v>
       </c>
       <c r="K30">
-        <v>1.4187072911011398</v>
+        <v>1.4467330675027483</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1182,13 +1252,13 @@
         <v>2883</v>
       </c>
       <c r="I31">
-        <v>-1.8651656313667197e-7</v>
+        <v>-2.373622730262551e-9</v>
       </c>
       <c r="J31">
-        <v>-4.978889962062753e-7</v>
+        <v>-6.31001925288194e-9</v>
       </c>
       <c r="K31">
-        <v>1.4406101554259965</v>
+        <v>1.4629285398041547</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1217,13 +1287,13 @@
         <v>3072</v>
       </c>
       <c r="I32">
-        <v>-4.2222114401495075e-8</v>
+        <v>-9.350583449441962e-10</v>
       </c>
       <c r="J32">
-        <v>-4.7554801444324624e-7</v>
+        <v>-6.025798337639933e-9</v>
       </c>
       <c r="K32">
-        <v>1.4736654837607013</v>
+        <v>1.4902734141977079</v>
       </c>
     </row>
   </sheetData>
